--- a/video-film-editing/output/09 4 Senarai Bukti Proses Kerja + Lampiran 4 Perakuan Pembimbing/4 Senarai Bukti Proses Kerja (IT-072).xlsx
+++ b/video-film-editing/output/09 4 Senarai Bukti Proses Kerja + Lampiran 4 Perakuan Pembimbing/4 Senarai Bukti Proses Kerja (IT-072).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38400" yWindow="-2480" windowWidth="38400" windowHeight="21600" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GARIS PANDUAN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARAI BUKTI PROSES KERJA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Susunan Semula PK ke CU-WA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="GARIS PANDUAN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SENARAI BUKTI PROSES KERJA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Susunan Semula PK ke CU-WA" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Aptos Narrow"/>
       <color theme="1"/>
@@ -111,8 +111,11 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -149,6 +152,12 @@
         <bgColor rgb="FF60CBF3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -379,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -475,6 +484,111 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -756,18 +870,21 @@
   <dimension ref="A1:A96"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="87.33203125" customWidth="1" style="2" min="1" max="1"/>
+    <col width="60" customWidth="1" style="2" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>GARIS PANDUAN: PENYEDIAAN SENARAI BUKTI PROSES KERJA UNTUK FAIL KOMPILASI BAKAT ADI</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="46" t="n"/>
+    </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="47" t="inlineStr">
         <is>
           <t>🎯 TUJUAN</t>
         </is>
@@ -780,71 +897,80 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="46" t="n"/>
+    </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>✅ Langkah 1: Rujuk NOSS Matrik</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>Buka dokumen NOSS Matrik yang berkaitan dengan bidang kemahiran bakat.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Kenalpasti jumlah Proses Kerja sebenar yang digunakan oleh syarikat. Mula dengan P01 hingga P0X yang akhir sekali. </t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>Semak tanda ✔️ dalam matriks untuk mengenalpasti  CU dan WA yang berkait dengan setiap proses kerja.</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="46" t="n"/>
+    </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="48" t="inlineStr">
         <is>
           <t>✅ Langkah 2: Tetapkan Kod &amp; Tajuk Proses Kerja</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="49" t="inlineStr">
         <is>
           <t>Tetapkan kod proses kerja bermula dari P01 dan seterusnya (contoh: P01, P02, P03…) mengikut susunan aktiviti sebenar syarikat.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>Namakan proses tersebut berdasarkan amalan kerja sebenar (contoh: “Aktiviti Jualan di Roadshow”, “Menangani Aduan Pelanggan”).</t>
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="46" t="n"/>
+    </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>✅ Langkah 3: Senaraikan Bukti Kerja Sebenar</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Untuk setiap proses kerja:</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>Senaraikan dokumen atau bahan bukti yang boleh dikumpulkan oleh bakat, seperti:
 Borang kerja, laporan, gambar, video, rekod sistem, invois, resit, atau e-mel kerja.</t>
@@ -852,7 +978,7 @@
       </c>
     </row>
     <row r="18" ht="80" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="49" t="inlineStr">
         <is>
           <t>Setiap bukti mesti disertakan dengan:
 Kod Proses Kerja (cth: P01)
@@ -862,202 +988,343 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="46" t="n"/>
+    </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="48" t="inlineStr">
         <is>
           <t>✅ Langkah 4: Label Pada Dokumen Bukti</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Setiap bukti kerja MESTI DILABEL secara jelas dan lengkap:</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="50" t="inlineStr">
         <is>
           <t>Contoh Label Dokumen:</t>
         </is>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="49" t="inlineStr">
         <is>
           <t>🔖 Kod Proses Kerja: P02</t>
         </is>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="49" t="inlineStr">
         <is>
           <t>🔖 Kod Bukti: 4</t>
         </is>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="49" t="inlineStr">
         <is>
           <t>🔖 Kod CU-WA: C02-W03</t>
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="46" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="46" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="51" t="inlineStr">
         <is>
           <t>📄 CONTOH FORMAT SENARAI BUKTI (untuk rujukan pembimbing dan pengajar)</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="46" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="46" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="46" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="46" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="46" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="46" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="46" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="46" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="46" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="46" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="46" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="46" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="46" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="46" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="46" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="46" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="46" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="46" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="46" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="46" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="46" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="46" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="46" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="46" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="46" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="46" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="46" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="46" t="n"/>
+    </row>
     <row r="57">
-      <c r="A57" s="15" t="inlineStr">
+      <c r="A57" s="51" t="inlineStr">
         <is>
           <t>✅ Jenis Bukti Kerja</t>
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="46" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="46" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="46" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="46" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="46" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="46" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="46" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="46" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="46" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="46" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="46" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="46" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="46" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="46" t="n"/>
+    </row>
     <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="12" t="inlineStr">
         <is>
           <t>💡 Nota: Gambar atau video boleh disertakan, tetapi mestilah disokong dengan bukti kukuh yang sah seperti laporan bertulis, borang atau resit.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="n"/>
+      <c r="A73" s="12" t="n"/>
     </row>
     <row r="74" ht="19" customHeight="1">
-      <c r="A74" s="16" t="inlineStr">
+      <c r="A74" s="52" t="inlineStr">
         <is>
           <t>🎯 Keutamaan Bukti</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="A75" s="50" t="inlineStr">
         <is>
           <t>1. Utamakan bukti bertulis hitam putih (black &amp; white) seperti:</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="49" t="inlineStr">
         <is>
           <t>Borang rasmi</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="49" t="inlineStr">
         <is>
           <t>Laporan bertulis</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="49" t="inlineStr">
         <is>
           <t>Resit transaksi</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="49" t="inlineStr">
         <is>
           <t>Cetakan sistem</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="49" t="inlineStr">
         <is>
           <t>Memo jabatan</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n"/>
+      <c r="A81" s="53" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="49" t="inlineStr">
         <is>
           <t>2. Bukti tidak kukuh tidak boleh berdiri sendiri.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n"/>
+      <c r="A83" s="53" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="49" t="inlineStr">
         <is>
           <t>3. Jika gambar/video digunakan, nyatakan:</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="A85" s="50" t="inlineStr">
         <is>
           <t>Tarikh, tempat dan tugasan yang dijalankan</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+      <c r="A86" s="50" t="inlineStr">
         <is>
           <t>Siapa yang mengesahkan aktiviti tersebut (cth: penyelia, ketua jabatan)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="n"/>
+      <c r="A87" s="12" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="46" t="n"/>
     </row>
     <row r="89" ht="19" customHeight="1">
-      <c r="A89" s="16" t="inlineStr">
+      <c r="A89" s="52" t="inlineStr">
         <is>
           <t>📌 NOTA TAMBAHAN UNTUK PEMBIMBING:</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="49" t="inlineStr">
         <is>
           <t>Bimbingan awal perlu meliputi cara mengenal pasti bukti yang sah dan relevan.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="49" t="inlineStr">
         <is>
           <t>Gunakan NOSS Matrik untuk menyemak kesesuaian pemetaan CU-WA ↔ Proses Kerja.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="49" t="inlineStr">
         <is>
           <t>Pastikan semua bukti fizikal atau digital disusun mengikut turutan Proses Kerja — bukan ikut susunan CU.</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="49" t="inlineStr">
         <is>
           <t>Pastikan semua dokumen bukti dilabel dengan Kod Proses Kerja, Kod Bukti, dan Kod CU-WA sebelum dikompilasikan.</t>
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="46" t="n"/>
+    </row>
     <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="17" t="inlineStr">
+      <c r="A95" s="51" t="inlineStr">
         <is>
           <t>✅ Contoh Label pada Bukti Proses Kerja</t>
         </is>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
+      <c r="A96" s="12" t="inlineStr">
         <is>
           <t>Label Tajuk Bukti, Kod Bukti dan Kod CU-WA pada bahagian kanan atas.</t>
         </is>
@@ -1077,16 +1344,16 @@
   <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="13.6640625" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="7.83203125" customWidth="1" min="3" max="3"/>
-    <col width="35.5" customWidth="1" min="4" max="4"/>
-    <col width="46.5" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
     <col width="8.6640625" customWidth="1" min="6" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="19" customHeight="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>Senarai Bukti Aktiviti Kerja</t>
         </is>
@@ -1097,690 +1364,712 @@
       <c r="E1" s="44" t="n"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>No Proses Kerja</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="55" t="inlineStr">
         <is>
           <t>Tajuk Proses Kerja</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="55" t="inlineStr">
         <is>
           <t>No Bukti</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="55" t="inlineStr">
         <is>
           <t>Tajuk Bukti (Evidence Document Name)</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="55" t="inlineStr">
         <is>
           <t>Mapping CU-WA (Based on Noss Matrik VS Proses Kerja)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="56" t="inlineStr">
         <is>
           <t>P01</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="57" t="inlineStr">
         <is>
           <t>Terima job brief &amp; analisis skrip projek</t>
         </is>
       </c>
-      <c r="C3" s="23" t="n">
+      <c r="C3" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="59" t="inlineStr">
         <is>
           <t>Job Description Bakat (jawatan Editor) (Dokumen HR)</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="60" t="inlineStr">
         <is>
           <t>C01-W01, C01-W02</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="19" t="n"/>
-      <c r="B4" s="20" t="n"/>
-      <c r="C4" s="19" t="n">
+      <c r="A4" s="56" t="n"/>
+      <c r="B4" s="57" t="n"/>
+      <c r="C4" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="61" t="inlineStr">
         <is>
           <t>Brief / skrip pelanggan yang diterima (salinan) (Dokumen projek)</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="60" t="inlineStr">
         <is>
           <t>C01-W01</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="19" t="n"/>
-      <c r="B5" s="20" t="n"/>
-      <c r="C5" s="19" t="n">
+      <c r="A5" s="56" t="n"/>
+      <c r="B5" s="57" t="n"/>
+      <c r="C5" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>Borang Analisis Projek &amp; Skrip (konsep, jenis audio, bahasa, output, tempoh) - ditandatangani Producer (Borang)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
         <is>
           <t>C01-W01</t>
         </is>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="19" t="n"/>
-      <c r="B6" s="20" t="n"/>
-      <c r="C6" s="23" t="n">
+      <c r="A6" s="56" t="n"/>
+      <c r="B6" s="57" t="n"/>
+      <c r="C6" s="58" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>Borang Analisis Konsep (genre, tema, VFX, SFX, muzik latar, teknik editing) (Borang)</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>C01-W02</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="19" t="n"/>
-      <c r="B7" s="20" t="n"/>
-      <c r="C7" s="19" t="n">
+      <c r="A7" s="56" t="n"/>
+      <c r="B7" s="57" t="n"/>
+      <c r="C7" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>Minit / nota mesyuarat pra-editing (Nota)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>C01-W01, C01-W02</t>
         </is>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>P02</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="57" t="inlineStr">
         <is>
           <t>Semak format sumber &amp; spesifikasi output</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>Media Log / senarai bahan projek (sumber, codec, frame rate, aspect ratio) (Cetakan sistem)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>C01-W03</t>
         </is>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="19" t="n"/>
-      <c r="B9" s="20" t="n"/>
-      <c r="C9" s="19" t="n">
+      <c r="A9" s="56" t="n"/>
+      <c r="B9" s="57" t="n"/>
+      <c r="C9" s="56" t="n">
         <v>7</v>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>Laporan semakan format vs spesifikasi output (termasuk keperluan up/down conversion) (Laporan)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>C01-W03, C01-W04</t>
         </is>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="19" t="n"/>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="19" t="n">
+      <c r="A10" s="56" t="n"/>
+      <c r="B10" s="57" t="n"/>
+      <c r="C10" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="61" t="inlineStr">
         <is>
           <t>Senarai shot diperlukan ikut skrip + e-mel pengesahan bahan lengkap / kurang (E-mel + senarai)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="60" t="inlineStr">
         <is>
           <t>C01-W04</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>P03</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="57" t="inlineStr">
         <is>
           <t>Sediakan aliran kerja &amp; jadual projek</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="58" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="59" t="inlineStr">
         <is>
           <t>Carta aliran kerja projek (offline -&gt; online -&gt; delivery) (Carta)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="60" t="inlineStr">
         <is>
           <t>C01-W05</t>
         </is>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="19" t="n"/>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="19" t="n">
+      <c r="A12" s="56" t="n"/>
+      <c r="B12" s="57" t="n"/>
+      <c r="C12" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="61" t="inlineStr">
         <is>
           <t>Jadual projek (milestone &amp; tarikh) disahkan Producer (Jadual)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="60" t="inlineStr">
         <is>
           <t>C01-W05</t>
         </is>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="19" t="n"/>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="19" t="n">
+      <c r="A13" s="56" t="n"/>
+      <c r="B13" s="57" t="n"/>
+      <c r="C13" s="56" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="61" t="inlineStr">
         <is>
           <t>Muka surat Log Book Suite Editing (pembukaan projek) (Log book)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>C05-W06</t>
         </is>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t>P04</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="57" t="inlineStr">
         <is>
           <t>Ingest, tukar format &amp; digitasi footage</t>
         </is>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="61" t="inlineStr">
         <is>
           <t>Ingest checklist / laporan pemindahan bahan ke server &amp; backup (Borang)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="60" t="inlineStr">
         <is>
           <t>C02-W03</t>
         </is>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="1" t="n"/>
-      <c r="C15" s="1" t="n">
+      <c r="A15" s="62" t="n"/>
+      <c r="B15" s="46" t="n"/>
+      <c r="C15" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>Screenshot struktur folder projek (server &amp; hard disk) (Gambar + borang)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="46" t="inlineStr">
         <is>
           <t>C02-W03</t>
         </is>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="42" t="inlineStr">
+      <c r="A16" s="63" t="inlineStr">
         <is>
           <t>Nota: semua bukti aktiviti kerja perlu disahkan oleh Pembimbing dan Cop Syarikat.</t>
         </is>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="B16" s="46" t="n"/>
+      <c r="C16" s="62" t="n">
         <v>14</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="46" t="inlineStr">
         <is>
           <t>Laporan transcode (format asal -&gt; format editing, nama fail, timecode) (Cetakan sistem)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="46" t="inlineStr">
         <is>
           <t>C02-W02</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr">
         <is>
           <t>P05</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Log footage &amp; susun bin</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="62" t="n">
         <v>15</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="46" t="inlineStr">
         <is>
           <t>Cue sheet / continuity sheet bertanda "good take" (Borang set)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="46" t="inlineStr">
         <is>
           <t>C02-W01</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="1" t="n"/>
-      <c r="C18" s="1" t="n">
+      <c r="A18" s="62" t="n"/>
+      <c r="B18" s="46" t="n"/>
+      <c r="C18" s="62" t="n">
         <v>16</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="46" t="inlineStr">
         <is>
           <t>Screenshot bin NLE berlabel ikut scene (Gambar + borang)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="46" t="inlineStr">
         <is>
           <t>C02-W04</t>
         </is>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="1" t="n"/>
-      <c r="C19" s="1" t="n">
+      <c r="A19" s="62" t="n"/>
+      <c r="B19" s="46" t="n"/>
+      <c r="C19" s="62" t="n">
         <v>17</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="46" t="inlineStr">
         <is>
           <t>Senarai best shot terpilih per scene (Senarai)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="46" t="inlineStr">
         <is>
           <t>C03-W01</t>
         </is>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t>P06</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="46" t="inlineStr">
         <is>
           <t>Bina rough cut</t>
         </is>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="62" t="n">
         <v>18</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="46" t="inlineStr">
         <is>
           <t>Screenshot timeline rough cut + tempoh (Gambar + borang)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="46" t="inlineStr">
         <is>
           <t>C03-W02</t>
         </is>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="1" t="n"/>
-      <c r="C21" s="1" t="n">
+      <c r="A21" s="62" t="n"/>
+      <c r="B21" s="46" t="n"/>
+      <c r="C21" s="62" t="n">
         <v>19</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="46" t="inlineStr">
         <is>
           <t>Borang semakan rough cut oleh Director (ulasan &amp; pembetulan) (Borang)</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="46" t="inlineStr">
         <is>
           <t>C03-W03</t>
         </is>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="1" t="n"/>
-      <c r="C22" s="1" t="n">
+      <c r="A22" s="62" t="n"/>
+      <c r="B22" s="46" t="n"/>
+      <c r="C22" s="62" t="n">
         <v>20</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="46" t="inlineStr">
         <is>
           <t>Pautan / QR export rough cut (versi bertarikh) (Fail)</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="46" t="inlineStr">
         <is>
           <t>C03-W02, C03-W03</t>
         </is>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="62" t="inlineStr">
         <is>
           <t>P07</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="46" t="inlineStr">
         <is>
           <t>Elemen AV &amp; final offline (EDL)</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="62" t="n">
         <v>21</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="46" t="inlineStr">
         <is>
           <t>Senarai elemen AV sementara (temp music, SFX, grafik placeholder) (Senarai)</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="46" t="inlineStr">
         <is>
           <t>C03-W04</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="1" t="n"/>
-      <c r="C24" s="1" t="n">
+      <c r="A24" s="62" t="n"/>
+      <c r="B24" s="46" t="n"/>
+      <c r="C24" s="62" t="n">
         <v>22</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="46" t="inlineStr">
         <is>
           <t>Borang approval rough cut / picture lock ditandatangani Director (Borang)</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="46" t="inlineStr">
         <is>
           <t>C03-W05</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="1" t="n"/>
-      <c r="C25" s="1" t="n">
+      <c r="A25" s="62" t="n"/>
+      <c r="B25" s="46" t="n"/>
+      <c r="C25" s="62" t="n">
         <v>23</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="46" t="inlineStr">
         <is>
           <t>Fail EDL / XML / AAF (cetakan muka pertama) (Cetakan sistem)</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="46" t="inlineStr">
         <is>
           <t>C03-W05, C05-W01</t>
         </is>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="1" t="n"/>
-      <c r="C26" s="1" t="n">
+      <c r="A26" s="62" t="n"/>
+      <c r="B26" s="46" t="n"/>
+      <c r="C26" s="62" t="n">
         <v>24</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="46" t="inlineStr">
         <is>
           <t>Screenshot conform online + laporan semakan tempoh akhir (Gambar + laporan)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="46" t="inlineStr">
         <is>
           <t>C05-W01</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="62" t="inlineStr">
         <is>
           <t>P08</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="46" t="inlineStr">
         <is>
           <t>Bersihkan &amp; susun trek audio</t>
         </is>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="62" t="n">
         <v>25</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="46" t="inlineStr">
         <is>
           <t>Screenshot susunan trek (dialog / foley / SFX / muzik) (Gambar + borang)</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="46" t="inlineStr">
         <is>
           <t>C04-W01, C04-W02</t>
         </is>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="1" t="n"/>
-      <c r="C28" s="1" t="n">
+      <c r="A28" s="62" t="n"/>
+      <c r="B28" s="46" t="n"/>
+      <c r="C28" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="46" t="inlineStr">
         <is>
           <t>Senarai semak clean sound &amp; foley per scene (Senarai semak)</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="46" t="inlineStr">
         <is>
           <t>C04-W01, C04-W02</t>
         </is>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="62" t="inlineStr">
         <is>
           <t>P09</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="46" t="inlineStr">
         <is>
           <t>Levelling &amp; audio mix</t>
         </is>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="62" t="n">
         <v>27</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="46" t="inlineStr">
         <is>
           <t>Laporan loudness (LUFS / true peak) sebelum &amp; selepas (Cetakan sistem)</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="46" t="inlineStr">
         <is>
           <t>C04-W03, C04-W04, C04-W05</t>
         </is>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="1" t="n"/>
-      <c r="C30" s="1" t="n">
+      <c r="A30" s="62" t="n"/>
+      <c r="B30" s="46" t="n"/>
+      <c r="C30" s="62" t="n">
         <v>28</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="46" t="inlineStr">
         <is>
           <t>Borang semakan audio Director (keseimbangan akhir) (Borang)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="46" t="inlineStr">
         <is>
           <t>C04-W06</t>
         </is>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="1" t="n"/>
-      <c r="C31" s="1" t="n">
+      <c r="A31" s="62" t="n"/>
+      <c r="B31" s="46" t="n"/>
+      <c r="C31" s="62" t="n">
         <v>29</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="46" t="inlineStr">
         <is>
           <t>Rekod export balanced audio ke online (nama fail, tarikh) (Log)</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="46" t="inlineStr">
         <is>
           <t>C04-W06</t>
         </is>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="46" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="46" t="inlineStr">
         <is>
           <t>Online: visual, titling &amp; colour</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="46" t="n">
         <v>30</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="46" t="inlineStr">
         <is>
           <t>Senarai grafik / lower-third / titling (ejaan disemak) (Senarai)</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="46" t="inlineStr">
         <is>
           <t>C05-W02, C05-W03</t>
         </is>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="C33" t="n">
+      <c r="A33" s="46" t="n"/>
+      <c r="B33" s="46" t="n"/>
+      <c r="C33" s="46" t="n">
         <v>31</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="46" t="inlineStr">
         <is>
           <t>Screenshot before/after colour correction + scope (Gambar + borang)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="46" t="inlineStr">
         <is>
           <t>C05-W04</t>
         </is>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="46" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="46" t="inlineStr">
         <is>
           <t>Gabung audio akhir &amp; hantar deliverable</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="46" t="n">
         <v>32</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="46" t="inlineStr">
         <is>
           <t>Borang QC akhir (audio sync, loudness, codec, resolusi) (Borang)</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="46" t="inlineStr">
         <is>
           <t>C05-W05, C05-W06</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="C35" t="n">
+      <c r="A35" s="46" t="n"/>
+      <c r="B35" s="46" t="n"/>
+      <c r="C35" s="46" t="n">
         <v>33</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="46" t="inlineStr">
         <is>
           <t>Delivery note / e-mel penghantaran kepada pelanggan (E-mel)</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="46" t="inlineStr">
         <is>
           <t>C05-W06</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="C36" t="n">
+      <c r="A36" s="46" t="n"/>
+      <c r="B36" s="46" t="n"/>
+      <c r="C36" s="46" t="n">
         <v>34</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="46" t="inlineStr">
         <is>
           <t>Muka surat Log Book Suite (penutupan projek) (Log book)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="46" t="inlineStr">
         <is>
           <t>C05-W06</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="46" t="inlineStr">
         <is>
           <t>Nota: semua bukti aktiviti kerja perlu disahkan oleh Pembimbing dan Cop Syarikat.</t>
         </is>
       </c>
+      <c r="B37" s="46" t="n"/>
+      <c r="C37" s="46" t="n"/>
+      <c r="D37" s="46" t="n"/>
+      <c r="E37" s="46" t="n"/>
     </row>
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
@@ -2764,377 +3053,388 @@
   <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="15.6640625" customWidth="1" min="1" max="1"/>
-    <col width="15.5" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>Rekod Bukti Pengalaman Kerja</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1" thickBot="1">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Senarai CU</t>
         </is>
       </c>
-      <c r="B2" s="33" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>Senarai WA</t>
         </is>
       </c>
-      <c r="C2" s="34" t="inlineStr">
+      <c r="C2" s="66" t="inlineStr">
         <is>
           <t>Senarai No Bukti</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="68" t="inlineStr">
         <is>
           <t>W01</t>
         </is>
       </c>
-      <c r="C3" s="35" t="inlineStr">
+      <c r="C3" s="69" t="inlineStr">
         <is>
           <t>1, 2, 3, 5</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="n"/>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="A4" s="70" t="n"/>
+      <c r="B4" s="71" t="inlineStr">
         <is>
           <t>W02</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="72" t="inlineStr">
         <is>
           <t>1, 4, 5</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1" thickBot="1">
-      <c r="A5" s="27" t="n"/>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="A5" s="73" t="n"/>
+      <c r="B5" s="74" t="inlineStr">
         <is>
           <t>W03</t>
         </is>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="75" t="inlineStr">
         <is>
           <t>6, 7</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="n"/>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="A6" s="67" t="n"/>
+      <c r="B6" s="68" t="inlineStr">
         <is>
           <t>W04</t>
         </is>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="76" t="inlineStr">
         <is>
           <t>7, 8</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n"/>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="A7" s="70" t="n"/>
+      <c r="B7" s="71" t="inlineStr">
         <is>
           <t>W05</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="75" t="inlineStr">
         <is>
           <t>9, 10</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1" thickBot="1">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="73" t="inlineStr">
         <is>
           <t>C02</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="74" t="inlineStr">
         <is>
           <t>W01</t>
         </is>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="75" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="n"/>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="A9" s="67" t="n"/>
+      <c r="B9" s="68" t="inlineStr">
         <is>
           <t>W02</t>
         </is>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="76" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n"/>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="A10" s="70" t="n"/>
+      <c r="B10" s="71" t="inlineStr">
         <is>
           <t>W03</t>
         </is>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="75" t="inlineStr">
         <is>
           <t>12, 13</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="n"/>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="A11" s="70" t="n"/>
+      <c r="B11" s="71" t="inlineStr">
         <is>
           <t>W04</t>
         </is>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C11" s="75" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1" thickBot="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="77" t="inlineStr">
         <is>
           <t>C03</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="78" t="inlineStr">
         <is>
           <t>W01</t>
         </is>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C12" s="75" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="n"/>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="A13" s="67" t="n"/>
+      <c r="B13" s="68" t="inlineStr">
         <is>
           <t>W02</t>
         </is>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C13" s="76" t="inlineStr">
         <is>
           <t>18, 20</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n"/>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="A14" s="70" t="n"/>
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>W03</t>
         </is>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="75" t="inlineStr">
         <is>
           <t>19, 20</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1" thickBot="1">
-      <c r="A15" s="27" t="n"/>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="A15" s="73" t="n"/>
+      <c r="B15" s="74" t="inlineStr">
         <is>
           <t>W04</t>
         </is>
       </c>
-      <c r="C15" s="39" t="inlineStr">
+      <c r="C15" s="79" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="46" t="n"/>
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>W05</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="46" t="inlineStr">
         <is>
           <t>22, 23</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>C04</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>W01</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="46" t="inlineStr">
         <is>
           <t>25, 26</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="46" t="n"/>
+      <c r="B18" s="46" t="inlineStr">
         <is>
           <t>W02</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="46" t="inlineStr">
         <is>
           <t>25, 26</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="46" t="n"/>
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>W03</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="46" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="46" t="n"/>
+      <c r="B20" s="46" t="inlineStr">
         <is>
           <t>W04</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="46" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="46" t="n"/>
+      <c r="B21" s="46" t="inlineStr">
         <is>
           <t>W05</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="46" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
+      <c r="A22" s="46" t="n"/>
+      <c r="B22" s="46" t="inlineStr">
         <is>
           <t>W06</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="46" t="inlineStr">
         <is>
           <t>28, 29</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="46" t="inlineStr">
         <is>
           <t>C05</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="46" t="inlineStr">
         <is>
           <t>W01</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="46" t="inlineStr">
         <is>
           <t>23, 24</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
+      <c r="A24" s="46" t="n"/>
+      <c r="B24" s="46" t="inlineStr">
         <is>
           <t>W02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="46" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="A25" s="46" t="n"/>
+      <c r="B25" s="46" t="inlineStr">
         <is>
           <t>W03</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="46" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="46" t="n"/>
+      <c r="B26" s="46" t="inlineStr">
         <is>
           <t>W04</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="46" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="46" t="n"/>
+      <c r="B27" s="46" t="inlineStr">
         <is>
           <t>W05</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="46" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="46" t="n"/>
+      <c r="B28" s="46" t="inlineStr">
         <is>
           <t>W06</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="46" t="inlineStr">
         <is>
           <t>11, 32, 33, 34</t>
         </is>
